--- a/TM_TC_ICD.xlsx
+++ b/TM_TC_ICD.xlsx
@@ -790,22 +790,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1013,14 +1013,14 @@
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1029,24 +1029,24 @@
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
@@ -1057,12 +1057,12 @@
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="45"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="47"/>
       <c r="G5" s="8" t="s">
         <v>9</v>
       </c>
@@ -1073,12 +1073,12 @@
     <row r="6" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
       <c r="G6" s="7" t="s">
         <v>11</v>
       </c>
@@ -1093,24 +1093,24 @@
       <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
@@ -1121,12 +1121,12 @@
       <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="45"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
@@ -1137,12 +1137,12 @@
     <row r="10" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1157,24 +1157,24 @@
       <c r="B11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="45"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="12"/>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
     </row>
@@ -1185,12 +1185,12 @@
       <c r="B13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="47"/>
       <c r="G13" s="8" t="s">
         <v>9</v>
       </c>
@@ -1201,12 +1201,12 @@
     <row r="14" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
       <c r="G14" s="7" t="s">
         <v>11</v>
       </c>
@@ -3495,8 +3495,8 @@
       <c r="D8" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3531,8 +3531,8 @@
       <c r="D10" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6839,12 +6839,12 @@
       <c r="C4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
     </row>
     <row r="5" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -6856,12 +6856,12 @@
       <c r="C5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="45"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="47"/>
     </row>
     <row r="6" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -6869,12 +6869,12 @@
       <c r="C6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
     </row>
     <row r="7" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
